--- a/data/industry/CFM/uMCP.xlsx
+++ b/data/industry/CFM/uMCP.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\PycharmProjects\AlternativeData\data\industry\CFM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\industry\CFM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86E65129-7202-452E-9970-60FB235A1490}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1E20242-F079-4B8B-835C-100036285C25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" tabRatio="666" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="666" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="uMCP(LPDDR4X + UFS2.2)4GB+128GB" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="9">
   <si>
     <t>Base Date</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -458,15 +458,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G33"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:G39"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.75" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.25" style="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.375" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.625" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.69921875" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.19921875" style="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.3984375" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.59765625" style="8" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="12"/>
-    <col min="7" max="7" width="11.25" style="12" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.19921875" style="12" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
@@ -1227,6 +1227,144 @@
       </c>
       <c r="G33" s="12">
         <v>91</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A34" s="10">
+        <v>46098</v>
+      </c>
+      <c r="B34" s="10">
+        <v>46098</v>
+      </c>
+      <c r="C34" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D34" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E34" s="12">
+        <v>91.1</v>
+      </c>
+      <c r="F34" s="12">
+        <v>94.2</v>
+      </c>
+      <c r="G34" s="12">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A35" s="10">
+        <v>46105</v>
+      </c>
+      <c r="B35" s="10">
+        <v>46105</v>
+      </c>
+      <c r="C35" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D35" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E35" s="12">
+        <v>91.1</v>
+      </c>
+      <c r="F35" s="12">
+        <v>94.2</v>
+      </c>
+      <c r="G35" s="12">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A36" s="10">
+        <v>46112</v>
+      </c>
+      <c r="B36" s="10">
+        <v>46112</v>
+      </c>
+      <c r="C36" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D36" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E36" s="12">
+        <v>91.1</v>
+      </c>
+      <c r="F36" s="12">
+        <v>94.2</v>
+      </c>
+      <c r="G36" s="12">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A37" s="10">
+        <v>46119</v>
+      </c>
+      <c r="B37" s="10">
+        <v>46119</v>
+      </c>
+      <c r="C37" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D37" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E37" s="12">
+        <v>91.1</v>
+      </c>
+      <c r="F37" s="12">
+        <v>94.2</v>
+      </c>
+      <c r="G37" s="12">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A38" s="10">
+        <v>46126</v>
+      </c>
+      <c r="B38" s="10">
+        <v>46126</v>
+      </c>
+      <c r="C38" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D38" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E38" s="12">
+        <v>91.1</v>
+      </c>
+      <c r="F38" s="12">
+        <v>94.2</v>
+      </c>
+      <c r="G38" s="12">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A39" s="10">
+        <v>46133</v>
+      </c>
+      <c r="B39" s="10">
+        <v>46133</v>
+      </c>
+      <c r="C39" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D39" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E39" s="12">
+        <v>91.1</v>
+      </c>
+      <c r="F39" s="12">
+        <v>94.2</v>
+      </c>
+      <c r="G39" s="12">
+        <v>93</v>
       </c>
     </row>
   </sheetData>
@@ -1237,15 +1375,15 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7BBFB96D-E0DC-4AFD-BE63-80A1B57B983E}">
-  <dimension ref="A1:G33"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:G39"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.75" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.25" style="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.375" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.625" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.69921875" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.19921875" style="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.3984375" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.59765625" style="8" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="9"/>
-    <col min="7" max="7" width="11.25" style="9" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.19921875" style="9" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
@@ -2006,6 +2144,144 @@
       </c>
       <c r="G33" s="9">
         <v>104</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A34" s="10">
+        <v>46098</v>
+      </c>
+      <c r="B34" s="10">
+        <v>46098</v>
+      </c>
+      <c r="C34" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D34" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E34" s="9">
+        <v>110.5</v>
+      </c>
+      <c r="F34" s="9">
+        <v>114</v>
+      </c>
+      <c r="G34" s="9">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A35" s="10">
+        <v>46105</v>
+      </c>
+      <c r="B35" s="10">
+        <v>46105</v>
+      </c>
+      <c r="C35" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D35" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E35" s="9">
+        <v>110.5</v>
+      </c>
+      <c r="F35" s="9">
+        <v>114</v>
+      </c>
+      <c r="G35" s="9">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A36" s="10">
+        <v>46112</v>
+      </c>
+      <c r="B36" s="10">
+        <v>46112</v>
+      </c>
+      <c r="C36" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D36" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E36" s="9">
+        <v>110.5</v>
+      </c>
+      <c r="F36" s="9">
+        <v>114</v>
+      </c>
+      <c r="G36" s="9">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A37" s="10">
+        <v>46119</v>
+      </c>
+      <c r="B37" s="10">
+        <v>46119</v>
+      </c>
+      <c r="C37" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D37" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E37" s="9">
+        <v>110.5</v>
+      </c>
+      <c r="F37" s="9">
+        <v>114</v>
+      </c>
+      <c r="G37" s="9">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A38" s="10">
+        <v>46126</v>
+      </c>
+      <c r="B38" s="10">
+        <v>46126</v>
+      </c>
+      <c r="C38" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D38" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E38" s="9">
+        <v>110.5</v>
+      </c>
+      <c r="F38" s="9">
+        <v>114</v>
+      </c>
+      <c r="G38" s="9">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A39" s="10">
+        <v>46133</v>
+      </c>
+      <c r="B39" s="10">
+        <v>46133</v>
+      </c>
+      <c r="C39" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D39" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E39" s="9">
+        <v>110.5</v>
+      </c>
+      <c r="F39" s="9">
+        <v>114</v>
+      </c>
+      <c r="G39" s="9">
+        <v>113</v>
       </c>
     </row>
   </sheetData>
@@ -2016,15 +2292,15 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0C4456A-BBDC-4FAF-8248-C787C433008C}">
-  <dimension ref="A1:G33"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:G39"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.75" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.25" style="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.375" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.625" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.69921875" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.19921875" style="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.3984375" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.59765625" style="8" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="14"/>
-    <col min="7" max="7" width="11.25" style="14" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.19921875" style="14" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
@@ -2785,6 +3061,144 @@
       </c>
       <c r="G33" s="14">
         <v>123</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A34" s="10">
+        <v>46098</v>
+      </c>
+      <c r="B34" s="10">
+        <v>46098</v>
+      </c>
+      <c r="C34" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D34" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E34" s="14">
+        <v>133</v>
+      </c>
+      <c r="F34" s="14">
+        <v>139</v>
+      </c>
+      <c r="G34" s="14">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A35" s="10">
+        <v>46105</v>
+      </c>
+      <c r="B35" s="10">
+        <v>46105</v>
+      </c>
+      <c r="C35" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D35" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E35" s="14">
+        <v>133</v>
+      </c>
+      <c r="F35" s="14">
+        <v>139</v>
+      </c>
+      <c r="G35" s="14">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A36" s="10">
+        <v>46112</v>
+      </c>
+      <c r="B36" s="10">
+        <v>46112</v>
+      </c>
+      <c r="C36" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D36" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E36" s="14">
+        <v>133</v>
+      </c>
+      <c r="F36" s="14">
+        <v>139</v>
+      </c>
+      <c r="G36" s="14">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A37" s="10">
+        <v>46119</v>
+      </c>
+      <c r="B37" s="10">
+        <v>46119</v>
+      </c>
+      <c r="C37" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D37" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E37" s="14">
+        <v>133</v>
+      </c>
+      <c r="F37" s="14">
+        <v>139</v>
+      </c>
+      <c r="G37" s="14">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A38" s="10">
+        <v>46126</v>
+      </c>
+      <c r="B38" s="10">
+        <v>46126</v>
+      </c>
+      <c r="C38" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D38" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E38" s="14">
+        <v>133</v>
+      </c>
+      <c r="F38" s="14">
+        <v>139</v>
+      </c>
+      <c r="G38" s="14">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A39" s="10">
+        <v>46133</v>
+      </c>
+      <c r="B39" s="10">
+        <v>46133</v>
+      </c>
+      <c r="C39" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D39" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E39" s="14">
+        <v>133</v>
+      </c>
+      <c r="F39" s="14">
+        <v>139</v>
+      </c>
+      <c r="G39" s="14">
+        <v>136</v>
       </c>
     </row>
   </sheetData>
@@ -2795,15 +3209,15 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8CFD6F9F-3CCA-4363-AD1B-10496D95E8DB}">
-  <dimension ref="A1:H33"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:H39"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.75" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.25" style="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.375" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.625" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.69921875" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.19921875" style="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.3984375" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.59765625" style="8" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="14"/>
-    <col min="7" max="7" width="11.25" style="14" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.19921875" style="14" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="9" style="15"/>
     <col min="9" max="16384" width="9" style="5"/>
   </cols>
@@ -3567,6 +3981,144 @@
         <v>150</v>
       </c>
     </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A34" s="10">
+        <v>46098</v>
+      </c>
+      <c r="B34" s="10">
+        <v>46098</v>
+      </c>
+      <c r="C34" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D34" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E34" s="14">
+        <v>162</v>
+      </c>
+      <c r="F34" s="14">
+        <v>165.5</v>
+      </c>
+      <c r="G34" s="14">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A35" s="10">
+        <v>46105</v>
+      </c>
+      <c r="B35" s="10">
+        <v>46105</v>
+      </c>
+      <c r="C35" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D35" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E35" s="14">
+        <v>162</v>
+      </c>
+      <c r="F35" s="14">
+        <v>165.5</v>
+      </c>
+      <c r="G35" s="14">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A36" s="10">
+        <v>46112</v>
+      </c>
+      <c r="B36" s="10">
+        <v>46112</v>
+      </c>
+      <c r="C36" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D36" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E36" s="14">
+        <v>162</v>
+      </c>
+      <c r="F36" s="14">
+        <v>165.5</v>
+      </c>
+      <c r="G36" s="14">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A37" s="10">
+        <v>46119</v>
+      </c>
+      <c r="B37" s="10">
+        <v>46119</v>
+      </c>
+      <c r="C37" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D37" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E37" s="14">
+        <v>162</v>
+      </c>
+      <c r="F37" s="14">
+        <v>165.5</v>
+      </c>
+      <c r="G37" s="14">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A38" s="10">
+        <v>46126</v>
+      </c>
+      <c r="B38" s="10">
+        <v>46126</v>
+      </c>
+      <c r="C38" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D38" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E38" s="14">
+        <v>162</v>
+      </c>
+      <c r="F38" s="14">
+        <v>165.5</v>
+      </c>
+      <c r="G38" s="14">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A39" s="10">
+        <v>46133</v>
+      </c>
+      <c r="B39" s="10">
+        <v>46133</v>
+      </c>
+      <c r="C39" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D39" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E39" s="14">
+        <v>162</v>
+      </c>
+      <c r="F39" s="14">
+        <v>165.5</v>
+      </c>
+      <c r="G39" s="14">
+        <v>163</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/industry/CFM/uMCP.xlsx
+++ b/data/industry/CFM/uMCP.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\industry\CFM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32FD053F-0C88-43A9-9FEE-AD14EC4E27A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2EB12B1-7E7D-4741-98A2-EDB0D3F964B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="666" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,38 +28,38 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="9">
   <si>
     <t>Base Date</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>Release Date</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>Time</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>Time Zone</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>Low</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>High</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>Average</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>UTC+8</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>UTC+8</t>
@@ -77,7 +77,7 @@
     <numFmt numFmtId="167" formatCode="_-* #,##0.0_-;\-* #,##0.0_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="168" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -93,13 +93,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Verdana"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="8"/>
       <name val="Calibri"/>
       <family val="3"/>
@@ -107,10 +100,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
+      <b/>
+      <sz val="11"/>
       <color theme="1"/>
-      <name val="Verdana"/>
+      <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -141,41 +136,41 @@
   </cellStyleXfs>
   <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="3" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="168" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="168" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="쉼표" xfId="1" builtinId="3"/>
@@ -458,14 +453,1138 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G45"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
+  <dimension ref="A1:G48"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="12.6640625" style="10" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14.21875" style="10" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12.44140625" style="7" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11.5546875" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="9" style="12"/>
+    <col min="5" max="6" width="9" style="9"/>
+    <col min="7" max="7" width="11.21875" style="9" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="9" style="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" s="6">
+        <v>45860</v>
+      </c>
+      <c r="B2" s="6">
+        <v>45860</v>
+      </c>
+      <c r="C2" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" s="9">
+        <v>14.6</v>
+      </c>
+      <c r="F2" s="9">
+        <v>17.7</v>
+      </c>
+      <c r="G2" s="9">
+        <v>16.5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" s="6">
+        <v>45867</v>
+      </c>
+      <c r="B3" s="6">
+        <v>45867</v>
+      </c>
+      <c r="C3" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3" s="9">
+        <v>17.600000000000001</v>
+      </c>
+      <c r="F3" s="9">
+        <v>20.7</v>
+      </c>
+      <c r="G3" s="9">
+        <v>19.5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" s="6">
+        <v>45874</v>
+      </c>
+      <c r="B4" s="6">
+        <v>45874</v>
+      </c>
+      <c r="C4" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E4" s="9">
+        <v>17.600000000000001</v>
+      </c>
+      <c r="F4" s="9">
+        <v>20.7</v>
+      </c>
+      <c r="G4" s="9">
+        <v>19.5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" s="6">
+        <v>45881</v>
+      </c>
+      <c r="B5" s="6">
+        <v>45881</v>
+      </c>
+      <c r="C5" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E5" s="9">
+        <v>17.600000000000001</v>
+      </c>
+      <c r="F5" s="9">
+        <v>20.7</v>
+      </c>
+      <c r="G5" s="9">
+        <v>19.5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" s="6">
+        <v>45888</v>
+      </c>
+      <c r="B6" s="6">
+        <v>45888</v>
+      </c>
+      <c r="C6" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E6" s="9">
+        <v>17.600000000000001</v>
+      </c>
+      <c r="F6" s="9">
+        <v>20.7</v>
+      </c>
+      <c r="G6" s="9">
+        <v>19.5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" s="6">
+        <v>45895</v>
+      </c>
+      <c r="B7" s="6">
+        <v>45895</v>
+      </c>
+      <c r="C7" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E7" s="9">
+        <v>17.600000000000001</v>
+      </c>
+      <c r="F7" s="9">
+        <v>20.7</v>
+      </c>
+      <c r="G7" s="9">
+        <v>19.5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" s="6">
+        <v>45902</v>
+      </c>
+      <c r="B8" s="6">
+        <v>45902</v>
+      </c>
+      <c r="C8" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E8" s="9">
+        <v>17.600000000000001</v>
+      </c>
+      <c r="F8" s="9">
+        <v>20.7</v>
+      </c>
+      <c r="G8" s="9">
+        <v>19.5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" s="6">
+        <v>45909</v>
+      </c>
+      <c r="B9" s="6">
+        <v>45909</v>
+      </c>
+      <c r="C9" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E9" s="9">
+        <v>17.600000000000001</v>
+      </c>
+      <c r="F9" s="9">
+        <v>20.7</v>
+      </c>
+      <c r="G9" s="9">
+        <v>19.5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" s="6">
+        <v>45916</v>
+      </c>
+      <c r="B10" s="6">
+        <v>45916</v>
+      </c>
+      <c r="C10" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E10" s="9">
+        <v>17.600000000000001</v>
+      </c>
+      <c r="F10" s="9">
+        <v>20.7</v>
+      </c>
+      <c r="G10" s="9">
+        <v>19.5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" s="6">
+        <v>45923</v>
+      </c>
+      <c r="B11" s="6">
+        <v>45923</v>
+      </c>
+      <c r="C11" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E11" s="9">
+        <v>18.600000000000001</v>
+      </c>
+      <c r="F11" s="9">
+        <v>21.7</v>
+      </c>
+      <c r="G11" s="9">
+        <v>20.5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" s="6">
+        <v>45930</v>
+      </c>
+      <c r="B12" s="6">
+        <v>45930</v>
+      </c>
+      <c r="C12" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E12" s="9">
+        <v>18.600000000000001</v>
+      </c>
+      <c r="F12" s="9">
+        <v>21.7</v>
+      </c>
+      <c r="G12" s="9">
+        <v>20.5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13" s="6">
+        <v>45944</v>
+      </c>
+      <c r="B13" s="6">
+        <v>45944</v>
+      </c>
+      <c r="C13" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D13" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E13" s="9">
+        <v>22.1</v>
+      </c>
+      <c r="F13" s="9">
+        <v>25.2</v>
+      </c>
+      <c r="G13" s="9">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14" s="6">
+        <v>45951</v>
+      </c>
+      <c r="B14" s="6">
+        <v>45951</v>
+      </c>
+      <c r="C14" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E14" s="9">
+        <v>22.1</v>
+      </c>
+      <c r="F14" s="9">
+        <v>25.2</v>
+      </c>
+      <c r="G14" s="9">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15" s="6">
+        <v>45958</v>
+      </c>
+      <c r="B15" s="6">
+        <v>45958</v>
+      </c>
+      <c r="C15" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E15" s="9">
+        <v>22.1</v>
+      </c>
+      <c r="F15" s="9">
+        <v>25.2</v>
+      </c>
+      <c r="G15" s="9">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16" s="6">
+        <v>45965</v>
+      </c>
+      <c r="B16" s="6">
+        <v>45965</v>
+      </c>
+      <c r="C16" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E16" s="9">
+        <v>28.1</v>
+      </c>
+      <c r="F16" s="9">
+        <v>31.2</v>
+      </c>
+      <c r="G16" s="9">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17" s="6">
+        <v>45972</v>
+      </c>
+      <c r="B17" s="6">
+        <v>45972</v>
+      </c>
+      <c r="C17" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D17" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E17" s="9">
+        <v>31.1</v>
+      </c>
+      <c r="F17" s="9">
+        <v>34.200000000000003</v>
+      </c>
+      <c r="G17" s="9">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18" s="6">
+        <v>45979</v>
+      </c>
+      <c r="B18" s="6">
+        <v>45979</v>
+      </c>
+      <c r="C18" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D18" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E18" s="9">
+        <v>37.1</v>
+      </c>
+      <c r="F18" s="9">
+        <v>40.200000000000003</v>
+      </c>
+      <c r="G18" s="9">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19" s="6">
+        <v>45986</v>
+      </c>
+      <c r="B19" s="6">
+        <v>45986</v>
+      </c>
+      <c r="C19" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D19" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E19" s="9">
+        <v>45.1</v>
+      </c>
+      <c r="F19" s="9">
+        <v>48.2</v>
+      </c>
+      <c r="G19" s="9">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20" s="6">
+        <v>45993</v>
+      </c>
+      <c r="B20" s="6">
+        <v>45993</v>
+      </c>
+      <c r="C20" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D20" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E20" s="9">
+        <v>52.1</v>
+      </c>
+      <c r="F20" s="9">
+        <v>55.2</v>
+      </c>
+      <c r="G20" s="9">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21" s="6">
+        <v>46000</v>
+      </c>
+      <c r="B21" s="6">
+        <v>46000</v>
+      </c>
+      <c r="C21" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D21" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E21" s="9">
+        <v>56.1</v>
+      </c>
+      <c r="F21" s="9">
+        <v>59.2</v>
+      </c>
+      <c r="G21" s="9">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22" s="6">
+        <v>46007</v>
+      </c>
+      <c r="B22" s="6">
+        <v>46007</v>
+      </c>
+      <c r="C22" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D22" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E22" s="9">
+        <v>56.1</v>
+      </c>
+      <c r="F22" s="9">
+        <v>59.2</v>
+      </c>
+      <c r="G22" s="9">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23" s="6">
+        <v>46014</v>
+      </c>
+      <c r="B23" s="6">
+        <v>46014</v>
+      </c>
+      <c r="C23" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D23" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E23" s="9">
+        <v>59.1</v>
+      </c>
+      <c r="F23" s="9">
+        <v>62.2</v>
+      </c>
+      <c r="G23" s="9">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24" s="6">
+        <v>46021</v>
+      </c>
+      <c r="B24" s="6">
+        <v>46021</v>
+      </c>
+      <c r="C24" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D24" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E24" s="9">
+        <v>59.1</v>
+      </c>
+      <c r="F24" s="9">
+        <v>62.2</v>
+      </c>
+      <c r="G24" s="9">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25" s="6">
+        <v>46028</v>
+      </c>
+      <c r="B25" s="6">
+        <v>46028</v>
+      </c>
+      <c r="C25" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D25" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E25" s="9">
+        <v>59.1</v>
+      </c>
+      <c r="F25" s="9">
+        <v>62.2</v>
+      </c>
+      <c r="G25" s="9">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26" s="10">
+        <v>46035</v>
+      </c>
+      <c r="B26" s="10">
+        <v>46035</v>
+      </c>
+      <c r="C26" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D26" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E26" s="9">
+        <v>64.099999999999994</v>
+      </c>
+      <c r="F26" s="9">
+        <v>67.2</v>
+      </c>
+      <c r="G26" s="9">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27" s="10">
+        <v>46042</v>
+      </c>
+      <c r="B27" s="10">
+        <v>46042</v>
+      </c>
+      <c r="C27" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D27" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E27" s="9">
+        <v>68.099999999999994</v>
+      </c>
+      <c r="F27" s="9">
+        <v>71.2</v>
+      </c>
+      <c r="G27" s="9">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28" s="6">
+        <v>46049</v>
+      </c>
+      <c r="B28" s="6">
+        <v>46049</v>
+      </c>
+      <c r="C28" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D28" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E28" s="9">
+        <v>70.099999999999994</v>
+      </c>
+      <c r="F28" s="9">
+        <v>73.2</v>
+      </c>
+      <c r="G28" s="9">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29" s="10">
+        <v>46056</v>
+      </c>
+      <c r="B29" s="10">
+        <v>46056</v>
+      </c>
+      <c r="C29" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D29" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E29" s="9">
+        <v>73.099999999999994</v>
+      </c>
+      <c r="F29" s="9">
+        <v>76.2</v>
+      </c>
+      <c r="G29" s="9">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="A30" s="10">
+        <v>46063</v>
+      </c>
+      <c r="B30" s="10">
+        <v>46063</v>
+      </c>
+      <c r="C30" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D30" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E30" s="9">
+        <v>73.099999999999994</v>
+      </c>
+      <c r="F30" s="9">
+        <v>76.2</v>
+      </c>
+      <c r="G30" s="9">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="A31" s="10">
+        <v>46077</v>
+      </c>
+      <c r="B31" s="10">
+        <v>46077</v>
+      </c>
+      <c r="C31" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D31" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E31" s="9">
+        <v>73.099999999999994</v>
+      </c>
+      <c r="F31" s="9">
+        <v>76.2</v>
+      </c>
+      <c r="G31" s="9">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
+      <c r="A32" s="10">
+        <v>46084</v>
+      </c>
+      <c r="B32" s="10">
+        <v>46084</v>
+      </c>
+      <c r="C32" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D32" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E32" s="9">
+        <v>89.1</v>
+      </c>
+      <c r="F32" s="9">
+        <v>92.2</v>
+      </c>
+      <c r="G32" s="9">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7">
+      <c r="A33" s="10">
+        <v>46091</v>
+      </c>
+      <c r="B33" s="10">
+        <v>46091</v>
+      </c>
+      <c r="C33" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D33" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E33" s="9">
+        <v>89.1</v>
+      </c>
+      <c r="F33" s="9">
+        <v>92.2</v>
+      </c>
+      <c r="G33" s="9">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7">
+      <c r="A34" s="10">
+        <v>46098</v>
+      </c>
+      <c r="B34" s="10">
+        <v>46098</v>
+      </c>
+      <c r="C34" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D34" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E34" s="9">
+        <v>91.1</v>
+      </c>
+      <c r="F34" s="9">
+        <v>94.2</v>
+      </c>
+      <c r="G34" s="9">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7">
+      <c r="A35" s="10">
+        <v>46105</v>
+      </c>
+      <c r="B35" s="10">
+        <v>46105</v>
+      </c>
+      <c r="C35" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D35" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E35" s="9">
+        <v>91.1</v>
+      </c>
+      <c r="F35" s="9">
+        <v>94.2</v>
+      </c>
+      <c r="G35" s="9">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7">
+      <c r="A36" s="10">
+        <v>46112</v>
+      </c>
+      <c r="B36" s="10">
+        <v>46112</v>
+      </c>
+      <c r="C36" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D36" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E36" s="9">
+        <v>91.1</v>
+      </c>
+      <c r="F36" s="9">
+        <v>94.2</v>
+      </c>
+      <c r="G36" s="9">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7">
+      <c r="A37" s="10">
+        <v>46119</v>
+      </c>
+      <c r="B37" s="10">
+        <v>46119</v>
+      </c>
+      <c r="C37" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D37" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E37" s="9">
+        <v>91.1</v>
+      </c>
+      <c r="F37" s="9">
+        <v>94.2</v>
+      </c>
+      <c r="G37" s="9">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7">
+      <c r="A38" s="10">
+        <v>46126</v>
+      </c>
+      <c r="B38" s="10">
+        <v>46126</v>
+      </c>
+      <c r="C38" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D38" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E38" s="9">
+        <v>91.1</v>
+      </c>
+      <c r="F38" s="9">
+        <v>94.2</v>
+      </c>
+      <c r="G38" s="9">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7">
+      <c r="A39" s="10">
+        <v>46133</v>
+      </c>
+      <c r="B39" s="10">
+        <v>46133</v>
+      </c>
+      <c r="C39" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D39" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E39" s="9">
+        <v>91.1</v>
+      </c>
+      <c r="F39" s="9">
+        <v>94.2</v>
+      </c>
+      <c r="G39" s="9">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
+      <c r="A40" s="10">
+        <v>46140</v>
+      </c>
+      <c r="B40" s="10">
+        <v>46140</v>
+      </c>
+      <c r="C40" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D40" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E40" s="9">
+        <v>91.1</v>
+      </c>
+      <c r="F40" s="9">
+        <v>94.2</v>
+      </c>
+      <c r="G40" s="9">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
+      <c r="A41" s="10">
+        <v>46154</v>
+      </c>
+      <c r="B41" s="10">
+        <v>46154</v>
+      </c>
+      <c r="C41" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D41" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E41" s="9">
+        <v>87.1</v>
+      </c>
+      <c r="F41" s="9">
+        <v>90.2</v>
+      </c>
+      <c r="G41" s="9">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
+      <c r="A42" s="10">
+        <v>46161</v>
+      </c>
+      <c r="B42" s="10">
+        <v>46161</v>
+      </c>
+      <c r="C42" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D42" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E42" s="9">
+        <v>87.1</v>
+      </c>
+      <c r="F42" s="9">
+        <v>90.2</v>
+      </c>
+      <c r="G42" s="9">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
+      <c r="A43" s="10">
+        <v>46168</v>
+      </c>
+      <c r="B43" s="10">
+        <v>46168</v>
+      </c>
+      <c r="C43" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D43" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E43" s="9">
+        <v>86.1</v>
+      </c>
+      <c r="F43" s="9">
+        <v>89.2</v>
+      </c>
+      <c r="G43" s="9">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
+      <c r="A44" s="10">
+        <v>46175</v>
+      </c>
+      <c r="B44" s="10">
+        <v>46175</v>
+      </c>
+      <c r="C44" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D44" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E44" s="9">
+        <v>86.1</v>
+      </c>
+      <c r="F44" s="9">
+        <v>89.2</v>
+      </c>
+      <c r="G44" s="9">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7">
+      <c r="A45" s="10">
+        <v>46182</v>
+      </c>
+      <c r="B45" s="10">
+        <v>46182</v>
+      </c>
+      <c r="C45" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D45" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E45" s="9">
+        <v>86.1</v>
+      </c>
+      <c r="F45" s="9">
+        <v>89.2</v>
+      </c>
+      <c r="G45" s="9">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7">
+      <c r="A46" s="10">
+        <v>46189</v>
+      </c>
+      <c r="B46" s="10">
+        <v>46189</v>
+      </c>
+      <c r="C46" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D46" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E46" s="9">
+        <v>89.1</v>
+      </c>
+      <c r="F46" s="9">
+        <v>92.2</v>
+      </c>
+      <c r="G46" s="9">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7">
+      <c r="A47" s="10">
+        <v>46196</v>
+      </c>
+      <c r="B47" s="10">
+        <v>46196</v>
+      </c>
+      <c r="C47" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D47" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E47" s="9">
+        <v>89.1</v>
+      </c>
+      <c r="F47" s="9">
+        <v>92.2</v>
+      </c>
+      <c r="G47" s="9">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7">
+      <c r="A48" s="10">
+        <v>46203</v>
+      </c>
+      <c r="B48" s="10">
+        <v>46203</v>
+      </c>
+      <c r="C48" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D48" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E48" s="9">
+        <v>89.1</v>
+      </c>
+      <c r="F48" s="9">
+        <v>92.2</v>
+      </c>
+      <c r="G48" s="9">
+        <v>91</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7BBFB96D-E0DC-4AFD-BE63-80A1B57B983E}">
+  <dimension ref="A1:G48"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="12.6640625" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.21875" style="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.44140625" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.5546875" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="9.5546875" style="12" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="11.21875" style="12" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="5"/>
   </cols>
@@ -507,13 +1626,13 @@
         <v>7</v>
       </c>
       <c r="E2" s="12">
-        <v>14.6</v>
+        <v>18.5</v>
       </c>
       <c r="F2" s="12">
-        <v>17.7</v>
+        <v>22</v>
       </c>
       <c r="G2" s="12">
-        <v>16.5</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -530,13 +1649,13 @@
         <v>7</v>
       </c>
       <c r="E3" s="12">
-        <v>17.600000000000001</v>
+        <v>22.5</v>
       </c>
       <c r="F3" s="12">
-        <v>20.7</v>
+        <v>26</v>
       </c>
       <c r="G3" s="12">
-        <v>19.5</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -553,13 +1672,13 @@
         <v>7</v>
       </c>
       <c r="E4" s="12">
-        <v>17.600000000000001</v>
+        <v>22.5</v>
       </c>
       <c r="F4" s="12">
-        <v>20.7</v>
+        <v>26</v>
       </c>
       <c r="G4" s="12">
-        <v>19.5</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -576,13 +1695,13 @@
         <v>7</v>
       </c>
       <c r="E5" s="12">
-        <v>17.600000000000001</v>
+        <v>22.5</v>
       </c>
       <c r="F5" s="12">
-        <v>20.7</v>
+        <v>26</v>
       </c>
       <c r="G5" s="12">
-        <v>19.5</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -599,13 +1718,13 @@
         <v>7</v>
       </c>
       <c r="E6" s="12">
-        <v>17.600000000000001</v>
+        <v>22.5</v>
       </c>
       <c r="F6" s="12">
-        <v>20.7</v>
+        <v>26</v>
       </c>
       <c r="G6" s="12">
-        <v>19.5</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -622,13 +1741,13 @@
         <v>7</v>
       </c>
       <c r="E7" s="12">
-        <v>17.600000000000001</v>
+        <v>22.5</v>
       </c>
       <c r="F7" s="12">
-        <v>20.7</v>
+        <v>26</v>
       </c>
       <c r="G7" s="12">
-        <v>19.5</v>
+        <v>25</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -645,13 +1764,13 @@
         <v>7</v>
       </c>
       <c r="E8" s="12">
-        <v>17.600000000000001</v>
+        <v>22.5</v>
       </c>
       <c r="F8" s="12">
-        <v>20.7</v>
+        <v>26</v>
       </c>
       <c r="G8" s="12">
-        <v>19.5</v>
+        <v>25</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -668,13 +1787,13 @@
         <v>7</v>
       </c>
       <c r="E9" s="12">
-        <v>17.600000000000001</v>
+        <v>22.5</v>
       </c>
       <c r="F9" s="12">
-        <v>20.7</v>
+        <v>26</v>
       </c>
       <c r="G9" s="12">
-        <v>19.5</v>
+        <v>25</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -691,13 +1810,13 @@
         <v>7</v>
       </c>
       <c r="E10" s="12">
-        <v>17.600000000000001</v>
+        <v>22.5</v>
       </c>
       <c r="F10" s="12">
-        <v>20.7</v>
+        <v>26</v>
       </c>
       <c r="G10" s="12">
-        <v>19.5</v>
+        <v>25</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -714,13 +1833,13 @@
         <v>7</v>
       </c>
       <c r="E11" s="12">
-        <v>18.600000000000001</v>
+        <v>23.8</v>
       </c>
       <c r="F11" s="12">
-        <v>21.7</v>
+        <v>27.3</v>
       </c>
       <c r="G11" s="12">
-        <v>20.5</v>
+        <v>26.3</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -737,13 +1856,13 @@
         <v>7</v>
       </c>
       <c r="E12" s="12">
-        <v>18.600000000000001</v>
+        <v>23.8</v>
       </c>
       <c r="F12" s="12">
-        <v>21.7</v>
+        <v>27.3</v>
       </c>
       <c r="G12" s="12">
-        <v>20.5</v>
+        <v>26.3</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -760,13 +1879,13 @@
         <v>7</v>
       </c>
       <c r="E13" s="12">
-        <v>22.1</v>
+        <v>27.5</v>
       </c>
       <c r="F13" s="12">
-        <v>25.2</v>
+        <v>31</v>
       </c>
       <c r="G13" s="12">
-        <v>24</v>
+        <v>30</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -783,13 +1902,13 @@
         <v>7</v>
       </c>
       <c r="E14" s="12">
-        <v>22.1</v>
+        <v>27.5</v>
       </c>
       <c r="F14" s="12">
-        <v>25.2</v>
+        <v>31</v>
       </c>
       <c r="G14" s="12">
-        <v>24</v>
+        <v>30</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -806,13 +1925,13 @@
         <v>7</v>
       </c>
       <c r="E15" s="12">
-        <v>22.1</v>
+        <v>27.5</v>
       </c>
       <c r="F15" s="12">
-        <v>25.2</v>
+        <v>31</v>
       </c>
       <c r="G15" s="12">
-        <v>24</v>
+        <v>30</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -829,13 +1948,13 @@
         <v>7</v>
       </c>
       <c r="E16" s="12">
-        <v>28.1</v>
+        <v>34.5</v>
       </c>
       <c r="F16" s="12">
-        <v>31.2</v>
+        <v>38</v>
       </c>
       <c r="G16" s="12">
-        <v>30</v>
+        <v>37</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -852,13 +1971,13 @@
         <v>7</v>
       </c>
       <c r="E17" s="12">
-        <v>31.1</v>
+        <v>38.5</v>
       </c>
       <c r="F17" s="12">
-        <v>34.200000000000003</v>
+        <v>42</v>
       </c>
       <c r="G17" s="12">
-        <v>33</v>
+        <v>41</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -875,13 +1994,13 @@
         <v>7</v>
       </c>
       <c r="E18" s="12">
-        <v>37.1</v>
+        <v>46.5</v>
       </c>
       <c r="F18" s="12">
-        <v>40.200000000000003</v>
+        <v>50</v>
       </c>
       <c r="G18" s="12">
-        <v>39</v>
+        <v>49</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -898,13 +2017,13 @@
         <v>7</v>
       </c>
       <c r="E19" s="12">
-        <v>45.1</v>
+        <v>54.5</v>
       </c>
       <c r="F19" s="12">
-        <v>48.2</v>
+        <v>58</v>
       </c>
       <c r="G19" s="12">
-        <v>47</v>
+        <v>57</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -921,13 +2040,13 @@
         <v>7</v>
       </c>
       <c r="E20" s="12">
-        <v>52.1</v>
+        <v>58.5</v>
       </c>
       <c r="F20" s="12">
-        <v>55.2</v>
+        <v>62</v>
       </c>
       <c r="G20" s="12">
-        <v>54</v>
+        <v>61</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -944,13 +2063,13 @@
         <v>7</v>
       </c>
       <c r="E21" s="12">
-        <v>56.1</v>
+        <v>63.5</v>
       </c>
       <c r="F21" s="12">
-        <v>59.2</v>
+        <v>67</v>
       </c>
       <c r="G21" s="12">
-        <v>58</v>
+        <v>66</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -967,13 +2086,13 @@
         <v>7</v>
       </c>
       <c r="E22" s="12">
-        <v>56.1</v>
+        <v>63.5</v>
       </c>
       <c r="F22" s="12">
-        <v>59.2</v>
+        <v>67</v>
       </c>
       <c r="G22" s="12">
-        <v>58</v>
+        <v>66</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -990,13 +2109,13 @@
         <v>7</v>
       </c>
       <c r="E23" s="12">
-        <v>59.1</v>
+        <v>66.5</v>
       </c>
       <c r="F23" s="12">
-        <v>62.2</v>
+        <v>70</v>
       </c>
       <c r="G23" s="12">
-        <v>61</v>
+        <v>69</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -1013,13 +2132,13 @@
         <v>7</v>
       </c>
       <c r="E24" s="12">
-        <v>59.1</v>
+        <v>66.5</v>
       </c>
       <c r="F24" s="12">
-        <v>62.2</v>
+        <v>70</v>
       </c>
       <c r="G24" s="12">
-        <v>61</v>
+        <v>69</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -1036,13 +2155,13 @@
         <v>7</v>
       </c>
       <c r="E25" s="12">
-        <v>59.1</v>
+        <v>66.5</v>
       </c>
       <c r="F25" s="12">
-        <v>62.2</v>
+        <v>70</v>
       </c>
       <c r="G25" s="12">
-        <v>61</v>
+        <v>69</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -1059,13 +2178,13 @@
         <v>7</v>
       </c>
       <c r="E26" s="12">
-        <v>64.099999999999994</v>
+        <v>79.5</v>
       </c>
       <c r="F26" s="12">
-        <v>67.2</v>
+        <v>83</v>
       </c>
       <c r="G26" s="12">
-        <v>66</v>
+        <v>82</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1082,13 +2201,13 @@
         <v>7</v>
       </c>
       <c r="E27" s="12">
-        <v>68.099999999999994</v>
+        <v>83.5</v>
       </c>
       <c r="F27" s="12">
-        <v>71.2</v>
+        <v>87</v>
       </c>
       <c r="G27" s="12">
-        <v>70</v>
+        <v>86</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1105,13 +2224,13 @@
         <v>8</v>
       </c>
       <c r="E28" s="12">
-        <v>70.099999999999994</v>
+        <v>85.5</v>
       </c>
       <c r="F28" s="12">
-        <v>73.2</v>
+        <v>89</v>
       </c>
       <c r="G28" s="12">
-        <v>72</v>
+        <v>88</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1128,13 +2247,13 @@
         <v>8</v>
       </c>
       <c r="E29" s="12">
-        <v>73.099999999999994</v>
+        <v>88.5</v>
       </c>
       <c r="F29" s="12">
-        <v>76.2</v>
+        <v>92</v>
       </c>
       <c r="G29" s="12">
-        <v>75</v>
+        <v>91</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1151,13 +2270,13 @@
         <v>8</v>
       </c>
       <c r="E30" s="12">
-        <v>73.099999999999994</v>
+        <v>88.5</v>
       </c>
       <c r="F30" s="12">
-        <v>76.2</v>
+        <v>92</v>
       </c>
       <c r="G30" s="12">
-        <v>75</v>
+        <v>91</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1174,13 +2293,13 @@
         <v>8</v>
       </c>
       <c r="E31" s="12">
-        <v>73.099999999999994</v>
+        <v>88.5</v>
       </c>
       <c r="F31" s="12">
-        <v>76.2</v>
+        <v>92</v>
       </c>
       <c r="G31" s="12">
-        <v>75</v>
+        <v>91</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1197,13 +2316,13 @@
         <v>8</v>
       </c>
       <c r="E32" s="12">
-        <v>89.1</v>
+        <v>101.5</v>
       </c>
       <c r="F32" s="12">
-        <v>92.2</v>
+        <v>105</v>
       </c>
       <c r="G32" s="12">
-        <v>91</v>
+        <v>104</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1220,13 +2339,13 @@
         <v>8</v>
       </c>
       <c r="E33" s="12">
-        <v>89.1</v>
+        <v>101.5</v>
       </c>
       <c r="F33" s="12">
-        <v>92.2</v>
+        <v>105</v>
       </c>
       <c r="G33" s="12">
-        <v>91</v>
+        <v>104</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1243,13 +2362,13 @@
         <v>8</v>
       </c>
       <c r="E34" s="12">
-        <v>91.1</v>
+        <v>110.5</v>
       </c>
       <c r="F34" s="12">
-        <v>94.2</v>
+        <v>114</v>
       </c>
       <c r="G34" s="12">
-        <v>93</v>
+        <v>113</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1266,13 +2385,13 @@
         <v>8</v>
       </c>
       <c r="E35" s="12">
-        <v>91.1</v>
+        <v>110.5</v>
       </c>
       <c r="F35" s="12">
-        <v>94.2</v>
+        <v>114</v>
       </c>
       <c r="G35" s="12">
-        <v>93</v>
+        <v>113</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1289,13 +2408,13 @@
         <v>8</v>
       </c>
       <c r="E36" s="12">
-        <v>91.1</v>
+        <v>110.5</v>
       </c>
       <c r="F36" s="12">
-        <v>94.2</v>
+        <v>114</v>
       </c>
       <c r="G36" s="12">
-        <v>93</v>
+        <v>113</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1312,13 +2431,13 @@
         <v>8</v>
       </c>
       <c r="E37" s="12">
-        <v>91.1</v>
+        <v>110.5</v>
       </c>
       <c r="F37" s="12">
-        <v>94.2</v>
+        <v>114</v>
       </c>
       <c r="G37" s="12">
-        <v>93</v>
+        <v>113</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1335,13 +2454,13 @@
         <v>8</v>
       </c>
       <c r="E38" s="12">
-        <v>91.1</v>
+        <v>110.5</v>
       </c>
       <c r="F38" s="12">
-        <v>94.2</v>
+        <v>114</v>
       </c>
       <c r="G38" s="12">
-        <v>93</v>
+        <v>113</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1358,13 +2477,13 @@
         <v>8</v>
       </c>
       <c r="E39" s="12">
-        <v>91.1</v>
+        <v>110.5</v>
       </c>
       <c r="F39" s="12">
-        <v>94.2</v>
+        <v>114</v>
       </c>
       <c r="G39" s="12">
-        <v>93</v>
+        <v>113</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1381,13 +2500,13 @@
         <v>8</v>
       </c>
       <c r="E40" s="12">
-        <v>91.1</v>
+        <v>110.5</v>
       </c>
       <c r="F40" s="12">
-        <v>94.2</v>
+        <v>114</v>
       </c>
       <c r="G40" s="12">
-        <v>93</v>
+        <v>113</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1404,13 +2523,13 @@
         <v>8</v>
       </c>
       <c r="E41" s="12">
-        <v>87.1</v>
+        <v>107.5</v>
       </c>
       <c r="F41" s="12">
-        <v>90.2</v>
+        <v>111</v>
       </c>
       <c r="G41" s="12">
-        <v>89</v>
+        <v>110</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1427,13 +2546,13 @@
         <v>8</v>
       </c>
       <c r="E42" s="12">
-        <v>87.1</v>
+        <v>107.5</v>
       </c>
       <c r="F42" s="12">
-        <v>90.2</v>
+        <v>111</v>
       </c>
       <c r="G42" s="12">
-        <v>89</v>
+        <v>110</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1450,13 +2569,13 @@
         <v>8</v>
       </c>
       <c r="E43" s="12">
-        <v>86.1</v>
+        <v>105.5</v>
       </c>
       <c r="F43" s="12">
-        <v>89.2</v>
+        <v>109</v>
       </c>
       <c r="G43" s="12">
-        <v>88</v>
+        <v>108</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1473,13 +2592,13 @@
         <v>8</v>
       </c>
       <c r="E44" s="12">
-        <v>86.1</v>
+        <v>105.5</v>
       </c>
       <c r="F44" s="12">
-        <v>89.2</v>
+        <v>109</v>
       </c>
       <c r="G44" s="12">
-        <v>88</v>
+        <v>108</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1496,1080 +2615,94 @@
         <v>8</v>
       </c>
       <c r="E45" s="12">
-        <v>86.1</v>
+        <v>105.5</v>
       </c>
       <c r="F45" s="12">
-        <v>89.2</v>
+        <v>109</v>
       </c>
       <c r="G45" s="12">
-        <v>88</v>
+        <v>108</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7">
+      <c r="A46" s="10">
+        <v>46189</v>
+      </c>
+      <c r="B46" s="10">
+        <v>46189</v>
+      </c>
+      <c r="C46" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D46" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E46" s="12">
+        <v>106.5</v>
+      </c>
+      <c r="F46" s="12">
+        <v>110</v>
+      </c>
+      <c r="G46" s="12">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7">
+      <c r="A47" s="10">
+        <v>46196</v>
+      </c>
+      <c r="B47" s="10">
+        <v>46196</v>
+      </c>
+      <c r="C47" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D47" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E47" s="12">
+        <v>106.5</v>
+      </c>
+      <c r="F47" s="12">
+        <v>110</v>
+      </c>
+      <c r="G47" s="12">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7">
+      <c r="A48" s="10">
+        <v>46203</v>
+      </c>
+      <c r="B48" s="10">
+        <v>46203</v>
+      </c>
+      <c r="C48" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D48" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E48" s="12">
+        <v>106.5</v>
+      </c>
+      <c r="F48" s="12">
+        <v>110</v>
+      </c>
+      <c r="G48" s="12">
+        <v>109</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7BBFB96D-E0DC-4AFD-BE63-80A1B57B983E}">
-  <dimension ref="A1:G45"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
-  <cols>
-    <col min="1" max="1" width="12.6640625" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.21875" style="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.44140625" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.5546875" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="9.5546875" style="9" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.21875" style="9" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="9" style="5"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:7">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7">
-      <c r="A2" s="6">
-        <v>45860</v>
-      </c>
-      <c r="B2" s="6">
-        <v>45860</v>
-      </c>
-      <c r="C2" s="7">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D2" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E2" s="9">
-        <v>18.5</v>
-      </c>
-      <c r="F2" s="9">
-        <v>22</v>
-      </c>
-      <c r="G2" s="9">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3" s="6">
-        <v>45867</v>
-      </c>
-      <c r="B3" s="6">
-        <v>45867</v>
-      </c>
-      <c r="C3" s="7">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D3" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E3" s="9">
-        <v>22.5</v>
-      </c>
-      <c r="F3" s="9">
-        <v>26</v>
-      </c>
-      <c r="G3" s="9">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4" s="6">
-        <v>45874</v>
-      </c>
-      <c r="B4" s="6">
-        <v>45874</v>
-      </c>
-      <c r="C4" s="7">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D4" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E4" s="9">
-        <v>22.5</v>
-      </c>
-      <c r="F4" s="9">
-        <v>26</v>
-      </c>
-      <c r="G4" s="9">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5" s="6">
-        <v>45881</v>
-      </c>
-      <c r="B5" s="6">
-        <v>45881</v>
-      </c>
-      <c r="C5" s="7">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D5" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E5" s="9">
-        <v>22.5</v>
-      </c>
-      <c r="F5" s="9">
-        <v>26</v>
-      </c>
-      <c r="G5" s="9">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6" s="6">
-        <v>45888</v>
-      </c>
-      <c r="B6" s="6">
-        <v>45888</v>
-      </c>
-      <c r="C6" s="7">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E6" s="9">
-        <v>22.5</v>
-      </c>
-      <c r="F6" s="9">
-        <v>26</v>
-      </c>
-      <c r="G6" s="9">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7" s="6">
-        <v>45895</v>
-      </c>
-      <c r="B7" s="6">
-        <v>45895</v>
-      </c>
-      <c r="C7" s="7">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D7" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E7" s="9">
-        <v>22.5</v>
-      </c>
-      <c r="F7" s="9">
-        <v>26</v>
-      </c>
-      <c r="G7" s="9">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8" s="6">
-        <v>45902</v>
-      </c>
-      <c r="B8" s="6">
-        <v>45902</v>
-      </c>
-      <c r="C8" s="7">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D8" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E8" s="9">
-        <v>22.5</v>
-      </c>
-      <c r="F8" s="9">
-        <v>26</v>
-      </c>
-      <c r="G8" s="9">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9" s="6">
-        <v>45909</v>
-      </c>
-      <c r="B9" s="6">
-        <v>45909</v>
-      </c>
-      <c r="C9" s="7">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D9" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E9" s="9">
-        <v>22.5</v>
-      </c>
-      <c r="F9" s="9">
-        <v>26</v>
-      </c>
-      <c r="G9" s="9">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10" s="6">
-        <v>45916</v>
-      </c>
-      <c r="B10" s="6">
-        <v>45916</v>
-      </c>
-      <c r="C10" s="7">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D10" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E10" s="9">
-        <v>22.5</v>
-      </c>
-      <c r="F10" s="9">
-        <v>26</v>
-      </c>
-      <c r="G10" s="9">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11" s="6">
-        <v>45923</v>
-      </c>
-      <c r="B11" s="6">
-        <v>45923</v>
-      </c>
-      <c r="C11" s="7">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D11" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E11" s="9">
-        <v>23.8</v>
-      </c>
-      <c r="F11" s="9">
-        <v>27.3</v>
-      </c>
-      <c r="G11" s="9">
-        <v>26.3</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12" s="6">
-        <v>45930</v>
-      </c>
-      <c r="B12" s="6">
-        <v>45930</v>
-      </c>
-      <c r="C12" s="7">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D12" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E12" s="9">
-        <v>23.8</v>
-      </c>
-      <c r="F12" s="9">
-        <v>27.3</v>
-      </c>
-      <c r="G12" s="9">
-        <v>26.3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13" s="6">
-        <v>45944</v>
-      </c>
-      <c r="B13" s="6">
-        <v>45944</v>
-      </c>
-      <c r="C13" s="7">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D13" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E13" s="9">
-        <v>27.5</v>
-      </c>
-      <c r="F13" s="9">
-        <v>31</v>
-      </c>
-      <c r="G13" s="9">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14" s="6">
-        <v>45951</v>
-      </c>
-      <c r="B14" s="6">
-        <v>45951</v>
-      </c>
-      <c r="C14" s="7">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D14" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E14" s="9">
-        <v>27.5</v>
-      </c>
-      <c r="F14" s="9">
-        <v>31</v>
-      </c>
-      <c r="G14" s="9">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15" s="6">
-        <v>45958</v>
-      </c>
-      <c r="B15" s="6">
-        <v>45958</v>
-      </c>
-      <c r="C15" s="7">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D15" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E15" s="9">
-        <v>27.5</v>
-      </c>
-      <c r="F15" s="9">
-        <v>31</v>
-      </c>
-      <c r="G15" s="9">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16" s="6">
-        <v>45965</v>
-      </c>
-      <c r="B16" s="6">
-        <v>45965</v>
-      </c>
-      <c r="C16" s="7">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D16" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E16" s="9">
-        <v>34.5</v>
-      </c>
-      <c r="F16" s="9">
-        <v>38</v>
-      </c>
-      <c r="G16" s="9">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17" s="6">
-        <v>45972</v>
-      </c>
-      <c r="B17" s="6">
-        <v>45972</v>
-      </c>
-      <c r="C17" s="7">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D17" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E17" s="9">
-        <v>38.5</v>
-      </c>
-      <c r="F17" s="9">
-        <v>42</v>
-      </c>
-      <c r="G17" s="9">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18" s="6">
-        <v>45979</v>
-      </c>
-      <c r="B18" s="6">
-        <v>45979</v>
-      </c>
-      <c r="C18" s="7">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D18" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E18" s="9">
-        <v>46.5</v>
-      </c>
-      <c r="F18" s="9">
-        <v>50</v>
-      </c>
-      <c r="G18" s="9">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19" s="6">
-        <v>45986</v>
-      </c>
-      <c r="B19" s="6">
-        <v>45986</v>
-      </c>
-      <c r="C19" s="7">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D19" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E19" s="9">
-        <v>54.5</v>
-      </c>
-      <c r="F19" s="9">
-        <v>58</v>
-      </c>
-      <c r="G19" s="9">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20" s="6">
-        <v>45993</v>
-      </c>
-      <c r="B20" s="6">
-        <v>45993</v>
-      </c>
-      <c r="C20" s="7">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D20" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E20" s="9">
-        <v>58.5</v>
-      </c>
-      <c r="F20" s="9">
-        <v>62</v>
-      </c>
-      <c r="G20" s="9">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21" s="6">
-        <v>46000</v>
-      </c>
-      <c r="B21" s="6">
-        <v>46000</v>
-      </c>
-      <c r="C21" s="7">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D21" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E21" s="9">
-        <v>63.5</v>
-      </c>
-      <c r="F21" s="9">
-        <v>67</v>
-      </c>
-      <c r="G21" s="9">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22" s="6">
-        <v>46007</v>
-      </c>
-      <c r="B22" s="6">
-        <v>46007</v>
-      </c>
-      <c r="C22" s="7">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D22" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E22" s="9">
-        <v>63.5</v>
-      </c>
-      <c r="F22" s="9">
-        <v>67</v>
-      </c>
-      <c r="G22" s="9">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23" s="6">
-        <v>46014</v>
-      </c>
-      <c r="B23" s="6">
-        <v>46014</v>
-      </c>
-      <c r="C23" s="7">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D23" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E23" s="9">
-        <v>66.5</v>
-      </c>
-      <c r="F23" s="9">
-        <v>70</v>
-      </c>
-      <c r="G23" s="9">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24" s="6">
-        <v>46021</v>
-      </c>
-      <c r="B24" s="6">
-        <v>46021</v>
-      </c>
-      <c r="C24" s="7">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D24" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E24" s="9">
-        <v>66.5</v>
-      </c>
-      <c r="F24" s="9">
-        <v>70</v>
-      </c>
-      <c r="G24" s="9">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="A25" s="6">
-        <v>46028</v>
-      </c>
-      <c r="B25" s="6">
-        <v>46028</v>
-      </c>
-      <c r="C25" s="7">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D25" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E25" s="9">
-        <v>66.5</v>
-      </c>
-      <c r="F25" s="9">
-        <v>70</v>
-      </c>
-      <c r="G25" s="9">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
-      <c r="A26" s="10">
-        <v>46035</v>
-      </c>
-      <c r="B26" s="10">
-        <v>46035</v>
-      </c>
-      <c r="C26" s="7">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D26" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E26" s="9">
-        <v>79.5</v>
-      </c>
-      <c r="F26" s="9">
-        <v>83</v>
-      </c>
-      <c r="G26" s="9">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
-      <c r="A27" s="10">
-        <v>46042</v>
-      </c>
-      <c r="B27" s="10">
-        <v>46042</v>
-      </c>
-      <c r="C27" s="7">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D27" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E27" s="9">
-        <v>83.5</v>
-      </c>
-      <c r="F27" s="9">
-        <v>87</v>
-      </c>
-      <c r="G27" s="9">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
-      <c r="A28" s="6">
-        <v>46049</v>
-      </c>
-      <c r="B28" s="6">
-        <v>46049</v>
-      </c>
-      <c r="C28" s="7">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D28" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="E28" s="9">
-        <v>85.5</v>
-      </c>
-      <c r="F28" s="9">
-        <v>89</v>
-      </c>
-      <c r="G28" s="9">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7">
-      <c r="A29" s="10">
-        <v>46056</v>
-      </c>
-      <c r="B29" s="10">
-        <v>46056</v>
-      </c>
-      <c r="C29" s="7">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D29" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="E29" s="9">
-        <v>88.5</v>
-      </c>
-      <c r="F29" s="9">
-        <v>92</v>
-      </c>
-      <c r="G29" s="9">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7">
-      <c r="A30" s="10">
-        <v>46063</v>
-      </c>
-      <c r="B30" s="10">
-        <v>46063</v>
-      </c>
-      <c r="C30" s="7">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D30" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="E30" s="9">
-        <v>88.5</v>
-      </c>
-      <c r="F30" s="9">
-        <v>92</v>
-      </c>
-      <c r="G30" s="9">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7">
-      <c r="A31" s="10">
-        <v>46077</v>
-      </c>
-      <c r="B31" s="10">
-        <v>46077</v>
-      </c>
-      <c r="C31" s="7">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D31" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="E31" s="9">
-        <v>88.5</v>
-      </c>
-      <c r="F31" s="9">
-        <v>92</v>
-      </c>
-      <c r="G31" s="9">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7">
-      <c r="A32" s="10">
-        <v>46084</v>
-      </c>
-      <c r="B32" s="10">
-        <v>46084</v>
-      </c>
-      <c r="C32" s="7">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D32" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="E32" s="9">
-        <v>101.5</v>
-      </c>
-      <c r="F32" s="9">
-        <v>105</v>
-      </c>
-      <c r="G32" s="9">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7">
-      <c r="A33" s="10">
-        <v>46091</v>
-      </c>
-      <c r="B33" s="10">
-        <v>46091</v>
-      </c>
-      <c r="C33" s="7">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D33" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="E33" s="9">
-        <v>101.5</v>
-      </c>
-      <c r="F33" s="9">
-        <v>105</v>
-      </c>
-      <c r="G33" s="9">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7">
-      <c r="A34" s="10">
-        <v>46098</v>
-      </c>
-      <c r="B34" s="10">
-        <v>46098</v>
-      </c>
-      <c r="C34" s="7">
-        <v>0.45833333333333298</v>
-      </c>
-      <c r="D34" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="E34" s="9">
-        <v>110.5</v>
-      </c>
-      <c r="F34" s="9">
-        <v>114</v>
-      </c>
-      <c r="G34" s="9">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7">
-      <c r="A35" s="10">
-        <v>46105</v>
-      </c>
-      <c r="B35" s="10">
-        <v>46105</v>
-      </c>
-      <c r="C35" s="7">
-        <v>0.45833333333333298</v>
-      </c>
-      <c r="D35" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="E35" s="9">
-        <v>110.5</v>
-      </c>
-      <c r="F35" s="9">
-        <v>114</v>
-      </c>
-      <c r="G35" s="9">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7">
-      <c r="A36" s="10">
-        <v>46112</v>
-      </c>
-      <c r="B36" s="10">
-        <v>46112</v>
-      </c>
-      <c r="C36" s="7">
-        <v>0.45833333333333298</v>
-      </c>
-      <c r="D36" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="E36" s="9">
-        <v>110.5</v>
-      </c>
-      <c r="F36" s="9">
-        <v>114</v>
-      </c>
-      <c r="G36" s="9">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7">
-      <c r="A37" s="10">
-        <v>46119</v>
-      </c>
-      <c r="B37" s="10">
-        <v>46119</v>
-      </c>
-      <c r="C37" s="7">
-        <v>0.45833333333333298</v>
-      </c>
-      <c r="D37" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="E37" s="9">
-        <v>110.5</v>
-      </c>
-      <c r="F37" s="9">
-        <v>114</v>
-      </c>
-      <c r="G37" s="9">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7">
-      <c r="A38" s="10">
-        <v>46126</v>
-      </c>
-      <c r="B38" s="10">
-        <v>46126</v>
-      </c>
-      <c r="C38" s="7">
-        <v>0.45833333333333298</v>
-      </c>
-      <c r="D38" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="E38" s="9">
-        <v>110.5</v>
-      </c>
-      <c r="F38" s="9">
-        <v>114</v>
-      </c>
-      <c r="G38" s="9">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7">
-      <c r="A39" s="10">
-        <v>46133</v>
-      </c>
-      <c r="B39" s="10">
-        <v>46133</v>
-      </c>
-      <c r="C39" s="7">
-        <v>0.45833333333333298</v>
-      </c>
-      <c r="D39" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="E39" s="9">
-        <v>110.5</v>
-      </c>
-      <c r="F39" s="9">
-        <v>114</v>
-      </c>
-      <c r="G39" s="9">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7">
-      <c r="A40" s="10">
-        <v>46140</v>
-      </c>
-      <c r="B40" s="10">
-        <v>46140</v>
-      </c>
-      <c r="C40" s="7">
-        <v>0.45833333333333298</v>
-      </c>
-      <c r="D40" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="E40" s="9">
-        <v>110.5</v>
-      </c>
-      <c r="F40" s="9">
-        <v>114</v>
-      </c>
-      <c r="G40" s="9">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7">
-      <c r="A41" s="10">
-        <v>46154</v>
-      </c>
-      <c r="B41" s="10">
-        <v>46154</v>
-      </c>
-      <c r="C41" s="7">
-        <v>0.45833333333333298</v>
-      </c>
-      <c r="D41" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="E41" s="9">
-        <v>107.5</v>
-      </c>
-      <c r="F41" s="9">
-        <v>111</v>
-      </c>
-      <c r="G41" s="9">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7">
-      <c r="A42" s="10">
-        <v>46161</v>
-      </c>
-      <c r="B42" s="10">
-        <v>46161</v>
-      </c>
-      <c r="C42" s="7">
-        <v>0.45833333333333298</v>
-      </c>
-      <c r="D42" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="E42" s="9">
-        <v>107.5</v>
-      </c>
-      <c r="F42" s="9">
-        <v>111</v>
-      </c>
-      <c r="G42" s="9">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7">
-      <c r="A43" s="10">
-        <v>46168</v>
-      </c>
-      <c r="B43" s="10">
-        <v>46168</v>
-      </c>
-      <c r="C43" s="7">
-        <v>0.45833333333333298</v>
-      </c>
-      <c r="D43" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="E43" s="9">
-        <v>105.5</v>
-      </c>
-      <c r="F43" s="9">
-        <v>109</v>
-      </c>
-      <c r="G43" s="9">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7">
-      <c r="A44" s="10">
-        <v>46175</v>
-      </c>
-      <c r="B44" s="10">
-        <v>46175</v>
-      </c>
-      <c r="C44" s="7">
-        <v>0.45833333333333298</v>
-      </c>
-      <c r="D44" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="E44" s="9">
-        <v>105.5</v>
-      </c>
-      <c r="F44" s="9">
-        <v>109</v>
-      </c>
-      <c r="G44" s="9">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7">
-      <c r="A45" s="10">
-        <v>46182</v>
-      </c>
-      <c r="B45" s="10">
-        <v>46182</v>
-      </c>
-      <c r="C45" s="7">
-        <v>0.45833333333333298</v>
-      </c>
-      <c r="D45" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="E45" s="9">
-        <v>105.5</v>
-      </c>
-      <c r="F45" s="9">
-        <v>109</v>
-      </c>
-      <c r="G45" s="9">
-        <v>108</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0C4456A-BBDC-4FAF-8248-C787C433008C}">
-  <dimension ref="A1:G45"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
+  <dimension ref="A1:G48"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="12.6640625" style="10" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14.21875" style="10" bestFit="1" customWidth="1"/>
@@ -3615,16 +3748,85 @@
         <v>133</v>
       </c>
     </row>
+    <row r="46" spans="1:7">
+      <c r="A46" s="10">
+        <v>46189</v>
+      </c>
+      <c r="B46" s="10">
+        <v>46189</v>
+      </c>
+      <c r="C46" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D46" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E46" s="14">
+        <v>131</v>
+      </c>
+      <c r="F46" s="14">
+        <v>137</v>
+      </c>
+      <c r="G46" s="14">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7">
+      <c r="A47" s="10">
+        <v>46196</v>
+      </c>
+      <c r="B47" s="10">
+        <v>46196</v>
+      </c>
+      <c r="C47" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D47" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E47" s="14">
+        <v>131</v>
+      </c>
+      <c r="F47" s="14">
+        <v>137</v>
+      </c>
+      <c r="G47" s="14">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7">
+      <c r="A48" s="10">
+        <v>46203</v>
+      </c>
+      <c r="B48" s="10">
+        <v>46203</v>
+      </c>
+      <c r="C48" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D48" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E48" s="14">
+        <v>131</v>
+      </c>
+      <c r="F48" s="14">
+        <v>137</v>
+      </c>
+      <c r="G48" s="14">
+        <v>134</v>
+      </c>
+    </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8CFD6F9F-3CCA-4363-AD1B-10496D95E8DB}">
-  <dimension ref="A1:H45"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
+  <dimension ref="A1:H48"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="12.6640625" style="10" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14.21875" style="10" bestFit="1" customWidth="1"/>
@@ -4672,8 +4874,77 @@
         <v>160</v>
       </c>
     </row>
+    <row r="46" spans="1:7">
+      <c r="A46" s="10">
+        <v>46189</v>
+      </c>
+      <c r="B46" s="10">
+        <v>46189</v>
+      </c>
+      <c r="C46" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D46" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E46" s="14">
+        <v>160</v>
+      </c>
+      <c r="F46" s="14">
+        <v>163.5</v>
+      </c>
+      <c r="G46" s="14">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7">
+      <c r="A47" s="10">
+        <v>46196</v>
+      </c>
+      <c r="B47" s="10">
+        <v>46196</v>
+      </c>
+      <c r="C47" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D47" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E47" s="14">
+        <v>160</v>
+      </c>
+      <c r="F47" s="14">
+        <v>163.5</v>
+      </c>
+      <c r="G47" s="14">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7">
+      <c r="A48" s="10">
+        <v>46203</v>
+      </c>
+      <c r="B48" s="10">
+        <v>46203</v>
+      </c>
+      <c r="C48" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D48" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E48" s="14">
+        <v>160</v>
+      </c>
+      <c r="F48" s="14">
+        <v>163.5</v>
+      </c>
+      <c r="G48" s="14">
+        <v>161</v>
+      </c>
+    </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>